--- a/inst/extdata/ard-spec/report.xlsx
+++ b/inst/extdata/ard-spec/report.xlsx
@@ -13,7 +13,8 @@
     <sheet name="footer" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="titles" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="footnotes" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="about" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tokens" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="about" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -81,7 +82,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">table / listing / figure; blank: table.
+          <t xml:space="preserve">table / listing / figure / user (the report's own code leaves `content`: a data frame, rtftable pages, rtfplot figures or a list of them); blank: table.
 Example: listing</t>
         </r>
       </text>
@@ -107,8 +108,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">The program's name, joined to program_dir for {PROGRAM}; blank: {output_id}.
-Example: {output_id}</t>
+          <t xml:space="preserve">The program's name, joined to program_dir for {PROGRAM}; blank: the file name of the program that runs, {output_id} only when none is found.
+Example: t_14_1_1.R</t>
         </r>
       </text>
     </comment>
@@ -230,6 +231,58 @@
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">A word drawn diagonally behind every page (rtf_document(watermark = )); blank: none.
+Example: DRAFT</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">A figure report: the figure's width in inches (rtf_figures(width_twips = )); blank: the figure's own.
+Example: 9</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">A figure report: the figure's height in inches (rtf_figures(height_twips = )); blank: the figure's own.
+Example: 5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">Where the report's ARD comes from: blank, its own ARD definition (the analyses rows of its output_id); import:&lt;file&gt;, an ARD made elsewhere and taken in (the file in the study's input/ard/ folder, read with tfl_read_ard()).
+Example: import:t_14_2_1_cro.json</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -402,12 +455,25 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
+          <t xml:space="preserve">The document's font (its font table); the study's row (blank output_id) is the company's, written once in the setup code; blank: rtfreporter's option (Courier).
+Example: Courier New</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
           <t xml:space="preserve">The body font size in half-points (18 = 9 pt); blank: rtfreporter's option.
 Example: 18</t>
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -420,7 +486,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="O1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -433,7 +499,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -446,7 +512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -459,7 +525,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="R1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -771,8 +837,57 @@
 </comments>
 </file>
 
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tflspec</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report a row belongs to. Blank: a study-wide default; a row naming a report replaces the default row with the same key (ARD analyses: the report the analysis serves).
+Example: T-14-1-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The token's name: upper case, a letter then letters, digits or _; not one of rtfreporter's own ({PAGE}, {PROGRAM}, {DATETIME} ...).
+Example: STUDY</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">What it becomes; (none) takes a default out for this report.
+Example: ABC-123</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t xml:space="preserve">key</t>
   </si>
@@ -831,6 +946,18 @@
     <t xml:space="preserve">page_footer</t>
   </si>
   <si>
+    <t xml:space="preserve">watermark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">figure_width_in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">figure_height_in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ard_source</t>
+  </si>
+  <si>
     <t xml:space="preserve">note</t>
   </si>
   <si>
@@ -897,6 +1024,9 @@
     <t xml:space="preserve">footer_dist_in</t>
   </si>
   <si>
+    <t xml:space="preserve">font</t>
+  </si>
+  <si>
     <t xml:space="preserve">font_size_half_points</t>
   </si>
   <si>
@@ -942,16 +1072,16 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">SPONSOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interim Analysis</t>
+    <t xml:space="preserve">Example Pharma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinical Study Report</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">PROTOCOL: XXX-0000</t>
+    <t xml:space="preserve">Study EX-001</t>
   </si>
   <si>
     <t xml:space="preserve">Page {PAGE} of {TOTAL_PAGES}</t>
@@ -966,58 +1096,58 @@
     <t xml:space="preserve">4</t>
   </si>
   <si>
-    <t xml:space="preserve">Table 14.1.1</t>
+    <t xml:space="preserve">Table 14.1.2</t>
   </si>
   <si>
     <t xml:space="preserve">5</t>
   </si>
   <si>
-    <t xml:space="preserve">Demographic Characteristics</t>
+    <t xml:space="preserve">Demographics and Baseline Characteristics</t>
   </si>
   <si>
     <t xml:space="preserve">6</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;Safety Analysis Set&gt;</t>
+    <t xml:space="preserve">Safety Population</t>
   </si>
   <si>
     <t xml:space="preserve">AE</t>
   </si>
   <si>
-    <t xml:space="preserve">Table 14.3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treatment-Emergent Adverse Events by System Organ Class and Preferred Term</t>
+    <t xml:space="preserve">Table 14.3.1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treatment-Emergent Adverse Events by System Organ Class, Preferred Term and Sex</t>
   </si>
   <si>
     <t xml:space="preserve">ORR</t>
   </si>
   <si>
-    <t xml:space="preserve">Table 14.2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary of Overall Response by Subgroup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;Full Analysis Set&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table 14.3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shift from Baseline to Worst Post-Baseline Grade</t>
+    <t xml:space="preserve">Table 14.2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response Rate by Subgroup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efficacy Population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 14.3.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratory Toxicity Grade: Shift from Baseline</t>
   </si>
   <si>
     <t xml:space="preserve">7</t>
   </si>
   <si>
-    <t xml:space="preserve">Table 14.4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary of Plasma Concentrations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;PK Analysis Set&gt;</t>
+    <t xml:space="preserve">Table 14.5.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary of Concentrations by Nominal Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pharmacokinetic Population</t>
   </si>
   <si>
     <t xml:space="preserve">99</t>
@@ -1026,28 +1156,31 @@
     <t xml:space="preserve">{PROGRAM}       Generated on: {DATETIME}</t>
   </si>
   <si>
-    <t xml:space="preserve">SD = Standard Deviation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subjects were counted once per system organ class and once per preferred term.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MedDRA version 27.1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Objective response rate: proportion of subjects with complete or partial response.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI = Confidence Interval.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Columns are the baseline grade, rows the worst post-baseline grade.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CV = Coefficient of variation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD = Standard deviation</t>
+    <t xml:space="preserve">SD: standard deviation; Min: minimum; Max: maximum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A subject is counted once in a system organ class and once in a preferred term.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coded with MedDRA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response: complete or partial response.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI: exact (Clopper-Pearson) confidence interval.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each column is a baseline grade; each row the worst grade after baseline.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SD: standard deviation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrations below the lower limit of quantification are set to zero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
   </si>
   <si>
     <t xml:space="preserve">spec_version</t>
@@ -1458,17 +1591,29 @@
       <c r="N1" t="s">
         <v>19</v>
       </c>
+      <c r="O1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2"/>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
@@ -1479,19 +1624,23 @@
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2"/>
-      <c r="N2" t="s">
-        <v>23</v>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
+      <c r="R2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B3"/>
       <c r="C3"/>
       <c r="D3"/>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F3"/>
       <c r="G3"/>
@@ -1501,13 +1650,17 @@
       <c r="K3"/>
       <c r="L3"/>
       <c r="M3"/>
-      <c r="N3" t="s">
-        <v>26</v>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
+      <c r="R3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B4"/>
       <c r="C4"/>
@@ -1517,18 +1670,22 @@
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J4"/>
       <c r="K4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L4"/>
       <c r="M4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1548,77 +1705,80 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="M1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="O1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="P1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="Q1" t="s">
-        <v>46</v>
+        <v>50</v>
+      </c>
+      <c r="R1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="I2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1626,10 +1786,11 @@
       <c r="M2"/>
       <c r="N2"/>
       <c r="O2"/>
-      <c r="P2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q2"/>
+      <c r="P2"/>
+      <c r="Q2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1648,50 +1809,50 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2"/>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D2"/>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D3"/>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C4"/>
       <c r="D4"/>
@@ -1699,49 +1860,49 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C8"/>
       <c r="D8"/>
@@ -1749,49 +1910,49 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C12"/>
       <c r="D12"/>
@@ -1799,49 +1960,49 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" t="s">
         <v>72</v>
-      </c>
-      <c r="B15" t="s">
-        <v>67</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C16"/>
       <c r="D16"/>
@@ -1849,49 +2010,49 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C20"/>
       <c r="D20"/>
@@ -1899,10 +2060,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C21"/>
       <c r="D21"/>
@@ -1910,40 +2071,40 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C23"/>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C24"/>
       <c r="D24" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E24"/>
     </row>
@@ -1964,103 +2125,103 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2"/>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -2082,16 +2243,16 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2111,53 +2272,53 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -2176,6 +2337,29 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <legacyDrawing r:id="rIdvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -2184,10 +2368,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/ard-spec/report.xlsx
+++ b/inst/extdata/ard-spec/report.xlsx
@@ -82,7 +82,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">table / listing / figure / user (the report's own code leaves `content`: a data frame, rtftable pages, rtfplot figures or a list of them); blank: table.
+          <t xml:space="preserve">table / listing / figure; blank: table. A step of the report may be its own code instead (data_code, content_code).
 Example: listing</t>
         </r>
       </text>
@@ -251,8 +251,8 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">A figure report: the figure's width in inches (rtf_figures(width_twips = )); blank: the figure's own.
-Example: 9</t>
+          <t xml:space="preserve">A figure report: the figure's width on the page -- a number of inches, or fit (the page's body); drawn and placed so (rtf_figures(width_twips = )). Blank: the figure's own size, as rtfreporter places it (tfl_fig_page_size()).
+Example: fit</t>
         </r>
       </text>
     </comment>
@@ -264,7 +264,7 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">A figure report: the figure's height in inches (rtf_figures(height_twips = )); blank: the figure's own.
+          <t xml:space="preserve">A figure report: the figure's height on the page -- a number of inches, or fit (the page's body less its title and footnote lines); drawn and placed so. Blank: the figure's own size (tfl_fig_page_size()).
 Example: 5</t>
         </r>
       </text>
@@ -277,12 +277,51 @@
             <color rgb="FF000000"/>
             <name val="Tahoma"/>
           </rPr>
-          <t xml:space="preserve">Where the report's ARD comes from: blank, its own ARD definition (the analyses rows of its output_id); import:&lt;file&gt;, an ARD made elsewhere and taken in (the file in the study's input/ard/ folder, read with tfl_read_ard()).
+          <t xml:space="preserve">Where the report's ARD comes from: blank (a figure: none), its own ARD definition (the analyses rows of its output_id; a figure: own); import:&lt;file&gt;, an ARD made elsewhere and taken in (the file in the study's input/ard/ folder, read with tfl_read_ard()); table:&lt;output_id&gt;, a figure's: that table's ARD.
 Example: import:t_14_2_1_cro.json</t>
         </r>
       </text>
     </comment>
     <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The page pattern the report uses: blank, Standard (the blank rows of report, page, header, footer, titles, footnotes and tokens); a name, that pattern -- the rows whose output_id is @&lt;name&gt;, which say only what differs from Standard. The report's own rows go over its pattern's.
+Example: Compact</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report's own code for its data step, instead of the definition: R that leaves data (a table, a listing) or df (a figure); the datasets the report registers and, when it reads its ARD, ard are in reach (tfl_check_code()). Blank: the definition makes the data.
+Example: df &lt;- advs |&gt; dplyr::filter(PARAMCD == "SYSBP")</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <name val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">The report's own code for its content step, instead of the definition: R that leaves content -- a table plan, a data frame, rtftable pages, a ggplot or rtfplot figure, or a list of them -- for the report step to dress. Blank: the definition makes the content.
+Example: content &lt;- ggplot2::ggplot(df) + ggplot2::geom_line()</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -887,7 +926,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
   <si>
     <t xml:space="preserve">key</t>
   </si>
@@ -958,6 +997,15 @@
     <t xml:space="preserve">ard_source</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data_code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">content_code</t>
+  </si>
+  <si>
     <t xml:space="preserve">note</t>
   </si>
   <si>
@@ -1081,7 +1129,7 @@
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">Study EX-001</t>
+    <t xml:space="preserve">Study XYZ-ONC-01</t>
   </si>
   <si>
     <t xml:space="preserve">Page {PAGE} of {TOTAL_PAGES}</t>
@@ -1126,10 +1174,10 @@
     <t xml:space="preserve">Table 14.2.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Response Rate by Subgroup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Efficacy Population</t>
+    <t xml:space="preserve">Objective Response Rate by Subgroup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efficacy Evaluable Population</t>
   </si>
   <si>
     <t xml:space="preserve">Table 14.3.4</t>
@@ -1156,7 +1204,7 @@
     <t xml:space="preserve">{PROGRAM}       Generated on: {DATETIME}</t>
   </si>
   <si>
-    <t xml:space="preserve">SD: standard deviation; Min: minimum; Max: maximum.</t>
+    <t xml:space="preserve">SD: standard deviation; Min: minimum; Max: maximum; ECOG: Eastern Cooperative Oncology Group.</t>
   </si>
   <si>
     <t xml:space="preserve">A subject is counted once in a system organ class and once in a preferred term.</t>
@@ -1165,7 +1213,7 @@
     <t xml:space="preserve">Coded with MedDRA.</t>
   </si>
   <si>
-    <t xml:space="preserve">Response: complete or partial response.</t>
+    <t xml:space="preserve">Response: a confirmed complete or partial response (RECIST 1.1).</t>
   </si>
   <si>
     <t xml:space="preserve">CI: exact (Clopper-Pearson) confidence interval.</t>
@@ -1603,17 +1651,26 @@
       <c r="R1" t="s">
         <v>23</v>
       </c>
+      <c r="S1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2"/>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
@@ -1628,19 +1685,22 @@
       <c r="O2"/>
       <c r="P2"/>
       <c r="Q2"/>
-      <c r="R2" t="s">
-        <v>27</v>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B3"/>
       <c r="C3"/>
       <c r="D3"/>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F3"/>
       <c r="G3"/>
@@ -1654,13 +1714,16 @@
       <c r="O3"/>
       <c r="P3"/>
       <c r="Q3"/>
-      <c r="R3" t="s">
-        <v>30</v>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B4"/>
       <c r="C4"/>
@@ -1670,22 +1733,25 @@
       <c r="G4"/>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J4"/>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L4"/>
       <c r="M4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="N4"/>
       <c r="O4"/>
       <c r="P4"/>
       <c r="Q4"/>
-      <c r="R4" t="s">
-        <v>34</v>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1705,80 +1771,80 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="N1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Q1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="R1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1788,7 +1854,7 @@
       <c r="O2"/>
       <c r="P2"/>
       <c r="Q2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="R2"/>
     </row>
@@ -1809,50 +1875,50 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
       <c r="A2"/>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D2"/>
       <c r="E2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D3"/>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C4"/>
       <c r="D4"/>
@@ -1860,49 +1926,49 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C8"/>
       <c r="D8"/>
@@ -1910,49 +1976,49 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C12"/>
       <c r="D12"/>
@@ -1960,49 +2026,49 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C16"/>
       <c r="D16"/>
@@ -2010,49 +2076,49 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C20"/>
       <c r="D20"/>
@@ -2060,10 +2126,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C21"/>
       <c r="D21"/>
@@ -2071,40 +2137,40 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C23"/>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C24"/>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E24"/>
     </row>
@@ -2125,103 +2191,103 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
       <c r="A2"/>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -2243,16 +2309,16 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -2272,53 +2338,53 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D2"/>
       <c r="E2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -2340,7 +2406,7 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -2368,10 +2434,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
